--- a/forms/trg/Formulir_TRG_core.xlsx
+++ b/forms/trg/Formulir_TRG_core.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B24)</f>
+        <f>COUNTA(Anggota!B5:B25)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F24)</f>
+        <f>COUNTA(Anggota!F5:F25)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr.Buchari Mengge, MA</t>
+          <t>Prof. Dr. Suparman Abdullah, M.Si</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Department Sociology Faculty of Social and political Science Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Urban and Coastal Sociology, Poverty and Social Exclusion, Community Empowerment</t>
+          <t>social planning, social capital, social conflict and sociology of maritime communities</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -939,7 +935,7 @@
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57761911000</t>
+          <t>57215895397</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -954,12 +950,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Suryanto, S.Sos., M.Si</t>
+          <t>Dr.Buchari Mengge, MA</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -969,7 +965,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Sociology of Development, Participatory Development Planning and Social Conflict</t>
+          <t>Urban and Coastal Sociology, Poverty and Social Exclusion, Community Empowerment</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -980,7 +976,7 @@
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>59137155500</t>
+          <t>57761911000</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -995,12 +991,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr.Mansyur Radjab,M.Si</t>
+          <t>Suryanto, S.Sos., M.Si</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1010,7 +1006,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Development Study, Social Research, Sociology of Education</t>
+          <t>Sociology of Development, Participatory Development Planning and Social Conflict</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1019,7 +1015,11 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="12" t="n"/>
       <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>59137155500</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1032,22 +1032,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ansar Arifin,M.S</t>
+          <t>Dr.Mansyur Radjab,M.Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Department Anthropology Faculty of Social and political Science Hasanuddin University</t>
+          <t>Department Sociology Faculty of Social and political Science Hasanuddin University</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Maritime Anthropology,Poverty Fisherman,Social Culture Fisherman</t>
+          <t>Development Study, Social Research, Sociology of Education</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1056,11 +1056,7 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>55407295900</t>
-        </is>
-      </c>
+      <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1073,22 +1069,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Austin Humphries</t>
+          <t>Prof. Dr. Ansar Arifin,M.S</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>University of Rhode Island</t>
+          <t>Department Anthropology Faculty of Social and political Science Hasanuddin University</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>coastal fisheries,social-ecological systems,habitat restoration,food security,stock assessment</t>
+          <t>Maritime Anthropology,Poverty Fisherman,Social Culture Fisherman</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1099,7 +1095,7 @@
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>37561405300</t>
+          <t>55407295900</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1114,22 +1110,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Adnan Achiruddin Saleh</t>
+          <t>Prof. Austin Humphries</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Institut Agama Islam Negeri Parepare</t>
+          <t>University of Rhode Island</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Social Psychology</t>
+          <t>coastal fisheries,social-ecological systems,habitat restoration,food security,stock assessment</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1138,7 +1134,11 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>37561405300</t>
+        </is>
+      </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1151,22 +1151,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Leni Gustiawati,</t>
+          <t>Adnan Achiruddin Saleh</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Department Sociology Faculty of Social and political Science Hasanuddin University</t>
+          <t>Institut Agama Islam Negeri Parepare</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>xxxx</t>
+          <t>Social Psychology</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Amiruddin Hamzah</t>
+          <t>Leni Gustiawati,</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1223,10 +1223,26 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="11" t="n"/>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Amiruddin Hamzah</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>xxxx</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>The Coastal Community Development Research Group (CORE) is an interdisciplinary initiative dedicated to promoting the sustainability, resilience, and empowerment of coastal communities. In response to the growing challenges of climate change, marine resource depletion, and socio-economic vulnerability, CORE seeks to bridge scientific knowledge, local wisdom, and policy innovation to develop effective solutions for coastal development.</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
@@ -1234,7 +1250,11 @@
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1423,15 +1443,32 @@
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="12" t="n"/>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
